--- a/要件定義シート.xlsx
+++ b/要件定義シート.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="要件定義書" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="要件定義書" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -328,6 +328,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
@@ -575,7 +579,7 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
     </row>
-    <row r="2" ht="154.5" customHeight="1">
+    <row r="2" ht="207.0" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -595,7 +599,7 @@
         <v>3.0</v>
       </c>
     </row>
-    <row r="3" ht="125.25" customHeight="1">
+    <row r="3" ht="186.75" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>10</v>
@@ -613,7 +617,7 @@
         <v>2.0</v>
       </c>
     </row>
-    <row r="4" ht="56.25" customHeight="1">
+    <row r="4" ht="75.0" customHeight="1">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>13</v>
@@ -631,7 +635,7 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="5" ht="78.0" customHeight="1">
+    <row r="5" ht="128.25" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
@@ -651,7 +655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" ht="307.5" customHeight="1">
+    <row r="6" ht="420.0" customHeight="1">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>21</v>
@@ -669,7 +673,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" ht="90.75" customHeight="1">
+    <row r="7" ht="108.75" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>24</v>
@@ -687,7 +691,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="279.0" customHeight="1">
+    <row r="8" ht="418.5" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
@@ -707,7 +711,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" ht="114.75" customHeight="1">
+    <row r="9" ht="157.5" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>30</v>
